--- a/Proyectos/Proyectos.xlsx
+++ b/Proyectos/Proyectos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\cotizador-web-mp\Proyectos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1466F369-0EB8-4162-8A94-241C61F0253A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD9981A-A7C3-4B22-B3F3-EE42FBF06955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{835DC9D8-6857-4F21-A726-3C93CCAB3C03}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="108">
   <si>
     <t>PROYECTO</t>
   </si>
@@ -345,13 +345,31 @@
   </si>
   <si>
     <t>https://drive.google.com/drive/folders/1LTL0Rttjnn8BLMCNyOhXScMODbuC0hUA?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1o72s8BBxu9_TSvA4N-9tzHER7CKI0OOI/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>LINK_PDF</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1QS_BqPDFeFyWkM2t_oeVENFJyDm4HS5i/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rDI4XS2rIHtQJktqmVm8FMbrMrL4ikem/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1gNEj6Zv05PVaE7BmjRyd2nPVnLhGVDZq/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1XR3fasST9Di4ssakxugt9_rnDL7ysDga/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -375,6 +393,14 @@
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -574,10 +600,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -591,8 +618,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -927,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52296A6F-29CA-48E9-B71C-2F11E9C03F57}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.77734375" bestFit="1" customWidth="1"/>
@@ -935,9 +966,10 @@
     <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="82.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -953,8 +985,11 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -970,8 +1005,11 @@
       <c r="E2" s="8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -987,8 +1025,11 @@
       <c r="E3" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>14</v>
       </c>
@@ -1004,8 +1045,11 @@
       <c r="E4" s="8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" s="15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
@@ -1021,8 +1065,11 @@
       <c r="E5" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" s="14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>21</v>
       </c>
@@ -1038,8 +1085,11 @@
       <c r="E6" s="8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>24</v>
       </c>
@@ -1056,7 +1106,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>27</v>
       </c>
@@ -1073,7 +1123,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>27</v>
       </c>
@@ -1090,7 +1140,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>31</v>
       </c>
@@ -1107,7 +1157,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>34</v>
       </c>
@@ -1124,7 +1174,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
@@ -1141,7 +1191,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>40</v>
       </c>
@@ -1158,7 +1208,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>42</v>
       </c>
@@ -1171,7 +1221,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>44</v>
       </c>
@@ -1184,7 +1234,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>46</v>
       </c>
@@ -1582,6 +1632,11 @@
     <hyperlink ref="E37" r:id="rId36" xr:uid="{12E413BB-BC88-480D-AF82-4C8DE4DF4CB2}"/>
     <hyperlink ref="E38" r:id="rId37" xr:uid="{916985DD-FEC6-41C1-A9D6-A9E6DFF473E1}"/>
     <hyperlink ref="E39" r:id="rId38" xr:uid="{459188E0-53E1-4DF8-868B-F349F2418CC9}"/>
+    <hyperlink ref="F2" r:id="rId39" xr:uid="{A14886E3-7086-448A-932B-0617C9E67B6B}"/>
+    <hyperlink ref="F3" r:id="rId40" xr:uid="{81144A1A-548C-4539-A749-1677BAA0E1B9}"/>
+    <hyperlink ref="F4" r:id="rId41" xr:uid="{21638768-309B-413F-908B-45831434D749}"/>
+    <hyperlink ref="F5" r:id="rId42" xr:uid="{31E4C781-CF33-4106-85CF-E142FFDCD240}"/>
+    <hyperlink ref="F6" r:id="rId43" xr:uid="{00F13436-D414-4435-9ABE-D66824AE730D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Proyectos/Proyectos.xlsx
+++ b/Proyectos/Proyectos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\cotizador-web-mp\Proyectos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD9981A-A7C3-4B22-B3F3-EE42FBF06955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD56A766-9CE6-4DDF-A7DA-3D92919531D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{835DC9D8-6857-4F21-A726-3C93CCAB3C03}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="139">
   <si>
     <t>PROYECTO</t>
   </si>
@@ -363,6 +363,99 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1XR3fasST9Di4ssakxugt9_rnDL7ysDga/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1efzl508yLIijiDJitk9Hf34KKElMtQdQ/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/14K2n86e2nY-Bk-3RSEXofKv65a8NrCJT/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1F-qApB896ooYeVb-qbr0HwpwR7HKfita/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1A26quLwg_aRfOrNBPkmAxBaHHUCfnP70/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1oTGSmq7mEscsgV78cWvroEqsRiWZF9du/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1z76mGTV_yjJyTdPM4UW40EAp6ExZ7ngD/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/13iXmX3COV1N88Rc9TSSjx44TBf8OIDay/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1UtIJpsR93lRKOWbnZi2MNdm8HRK2nn-o/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ZDV7cbzhcdnsQS_D4VF3MhxvTe0zy9Zs/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1aqN0Q4cCrxyPUHVRtF2IjBgUhGTHne62/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1nhUpBzdS0OQe95KjYnNKeWXCvwuUpZdv/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1J34VvXubxc0tQfuNwyDrkpDlyLxPyMKL/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bKswFcjrXx9TEAIDdBxE6PNbHqI1yDcp/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1iaR8mxrV8cUOdmDM-ZdFAx4GL8KfUHZa/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1LUWhp4806dRHUhY6KHkCZkY_rr0y2xpb/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1YY-1wEumdr6vP4zBxv_uVhmGhY7W0mkE/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1KctIr2WAjvaUnXbWUJR37Dl2ADqVck3f/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1xlr8S5LB4ibhOADqVUdf-p6pXGqkTEl-/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1IopbkiBsKSkrC3lEV_kelLd8NGr6cEq5/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1vNfkMxmsiiNdOSAh7oGo-TS82ZqwPrL4/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zPsAc9_ftX-RIN8Q3v6SbObzKe2hEJmL/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bSFHIl_H958E8KVhQuLJrCBqHaosa9tZ/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18DEf9U93ERFWDuKBOKH-_b9lc7wGJfcU/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Xsmrap1H6d0qWnz5q30pgrhoadEJOrRm/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1E48rmtsfvUkOiw2DPZ8quaUVFpgh9d90/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1kx6R6xJp5jKabesmh02K8dPRqZBH21ZO/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1saw9h3TrxTDzz8xGgYXZgj-8_vwiOPUu/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1WEvyMGpmtWre5lkrFHHxmRmWzRcZLHay/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/15WsN0zy-pUNXViSewzCJdYsiZrstE-kv/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DPWwLoGVk4e7klZuZunNLp5vW2OpeFbR/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Qh0Ge2SvNJrzbcZyaK2u2eXJ7d_43Tax/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
@@ -618,7 +711,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
@@ -1105,6 +1198,9 @@
       <c r="E7" s="8" t="s">
         <v>26</v>
       </c>
+      <c r="F7" s="14" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
@@ -1122,6 +1218,9 @@
       <c r="E8" s="8" t="s">
         <v>29</v>
       </c>
+      <c r="F8" s="14" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
@@ -1139,6 +1238,9 @@
       <c r="E9" s="8" t="s">
         <v>30</v>
       </c>
+      <c r="F9" s="14" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
@@ -1156,6 +1258,9 @@
       <c r="E10" s="8" t="s">
         <v>33</v>
       </c>
+      <c r="F10" s="14" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
@@ -1173,6 +1278,9 @@
       <c r="E11" s="8" t="s">
         <v>36</v>
       </c>
+      <c r="F11" s="14" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
@@ -1190,6 +1298,9 @@
       <c r="E12" s="8" t="s">
         <v>39</v>
       </c>
+      <c r="F12" s="14" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
@@ -1206,6 +1317,9 @@
       </c>
       <c r="E13" s="8" t="s">
         <v>41</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1220,6 +1334,9 @@
       <c r="E14" s="8" t="s">
         <v>43</v>
       </c>
+      <c r="F14" s="14" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
@@ -1233,6 +1350,9 @@
       <c r="E15" s="8" t="s">
         <v>45</v>
       </c>
+      <c r="F15" s="14" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
@@ -1246,8 +1366,11 @@
       <c r="E16" s="8" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16" s="14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>48</v>
       </c>
@@ -1261,8 +1384,11 @@
       <c r="E17" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17" s="14" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>52</v>
       </c>
@@ -1276,8 +1402,11 @@
       <c r="E18" s="8" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>55</v>
       </c>
@@ -1291,8 +1420,11 @@
       <c r="E19" s="8" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19" s="14" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>57</v>
       </c>
@@ -1306,8 +1438,11 @@
       <c r="E20" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F20" s="14" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>59</v>
       </c>
@@ -1321,8 +1456,11 @@
       <c r="E21" s="8" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21" s="14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>62</v>
       </c>
@@ -1336,8 +1474,11 @@
       <c r="E22" s="8" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F22" s="14" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>64</v>
       </c>
@@ -1351,8 +1492,11 @@
       <c r="E23" s="8" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F23" s="14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>66</v>
       </c>
@@ -1366,8 +1510,11 @@
       <c r="E24" s="8" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24" s="14" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>68</v>
       </c>
@@ -1381,8 +1528,11 @@
       <c r="E25" s="8" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F25" s="14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>71</v>
       </c>
@@ -1396,8 +1546,11 @@
       <c r="E26" s="8" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F26" s="14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>73</v>
       </c>
@@ -1411,8 +1564,11 @@
       <c r="E27" s="8" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F27" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>75</v>
       </c>
@@ -1426,8 +1582,11 @@
       <c r="E28" s="8" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F28" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>77</v>
       </c>
@@ -1441,8 +1600,11 @@
       <c r="E29" s="8" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F29" s="14" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>80</v>
       </c>
@@ -1456,8 +1618,11 @@
       <c r="E30" s="8" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F30" s="14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>82</v>
       </c>
@@ -1471,8 +1636,11 @@
       <c r="E31" s="8" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F31" s="14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>84</v>
       </c>
@@ -1486,8 +1654,11 @@
       <c r="E32" s="8" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F32" s="14" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>86</v>
       </c>
@@ -1501,8 +1672,11 @@
       <c r="E33" s="8" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F33" s="14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>89</v>
       </c>
@@ -1516,8 +1690,11 @@
       <c r="E34" s="8" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F34" s="14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>91</v>
       </c>
@@ -1531,8 +1708,11 @@
       <c r="E35" s="8" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F35" s="14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>93</v>
       </c>
@@ -1546,8 +1726,11 @@
       <c r="E36" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F36" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>95</v>
       </c>
@@ -1562,7 +1745,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>98</v>
       </c>
@@ -1576,8 +1759,11 @@
       <c r="E38" s="8" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F38" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
         <v>100</v>
       </c>
@@ -1590,6 +1776,9 @@
       </c>
       <c r="E39" s="12" t="s">
         <v>101</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1637,6 +1826,38 @@
     <hyperlink ref="F4" r:id="rId41" xr:uid="{21638768-309B-413F-908B-45831434D749}"/>
     <hyperlink ref="F5" r:id="rId42" xr:uid="{31E4C781-CF33-4106-85CF-E142FFDCD240}"/>
     <hyperlink ref="F6" r:id="rId43" xr:uid="{00F13436-D414-4435-9ABE-D66824AE730D}"/>
+    <hyperlink ref="F7" r:id="rId44" xr:uid="{97A23FDA-CA28-49C5-9E7C-1C094AA10832}"/>
+    <hyperlink ref="F8" r:id="rId45" xr:uid="{D828B513-5124-4515-8EEC-8E39A7DBAF57}"/>
+    <hyperlink ref="F9" r:id="rId46" xr:uid="{D36F8A00-75AE-42B7-AC23-92918F423337}"/>
+    <hyperlink ref="F10" r:id="rId47" xr:uid="{06D17B36-6CE2-4F73-8639-9349D51DE387}"/>
+    <hyperlink ref="F11" r:id="rId48" xr:uid="{7CA148BE-5DB7-4714-A9B8-B182A81E15A6}"/>
+    <hyperlink ref="F12" r:id="rId49" xr:uid="{BE7D34AB-FE57-40F0-BF41-41CDA395E642}"/>
+    <hyperlink ref="F13" r:id="rId50" xr:uid="{C999A5CD-2FAF-4ACA-B50D-D2427CF0E678}"/>
+    <hyperlink ref="F14" r:id="rId51" xr:uid="{707B9473-9C5C-47FB-B265-CD70D78022D2}"/>
+    <hyperlink ref="F15" r:id="rId52" xr:uid="{AA49FFCC-A227-470D-8E6D-F417C5F0ABEA}"/>
+    <hyperlink ref="F16" r:id="rId53" xr:uid="{BB02482C-C137-44D3-945E-C95B125A925C}"/>
+    <hyperlink ref="F17" r:id="rId54" xr:uid="{C9763593-0C6C-4FD0-B3BD-3746627B5B22}"/>
+    <hyperlink ref="F18" r:id="rId55" xr:uid="{AB456D75-9533-4581-9D69-B42851D4227E}"/>
+    <hyperlink ref="F19" r:id="rId56" xr:uid="{AE4522EF-FC98-4236-8FA7-075EB869C6DD}"/>
+    <hyperlink ref="F20" r:id="rId57" xr:uid="{087298F9-B845-4C0E-BF77-6E237FFE3924}"/>
+    <hyperlink ref="F21" r:id="rId58" xr:uid="{8CE228B7-155E-4B8A-A1E1-C62A9C3F61FD}"/>
+    <hyperlink ref="F22" r:id="rId59" xr:uid="{CB1FD313-0493-490A-87FF-652A7A0C8592}"/>
+    <hyperlink ref="F23" r:id="rId60" xr:uid="{2DD2060C-DF3D-4765-B1B0-B1B300CC777D}"/>
+    <hyperlink ref="F24" r:id="rId61" xr:uid="{4B52DA7C-C2E7-4947-95DC-05679DDEBBC9}"/>
+    <hyperlink ref="F25" r:id="rId62" xr:uid="{77ED9F19-64E3-4B47-99C3-570585F7B287}"/>
+    <hyperlink ref="F26" r:id="rId63" xr:uid="{268D5584-3CEC-4562-B251-E0AF51A682A1}"/>
+    <hyperlink ref="F27" r:id="rId64" xr:uid="{DCE86C7B-BFFC-47D3-A5DD-5BF7BD86FB92}"/>
+    <hyperlink ref="F28" r:id="rId65" xr:uid="{2C13EFFE-C633-47E3-8F69-5604F0580DC1}"/>
+    <hyperlink ref="F29" r:id="rId66" xr:uid="{0ECBAC06-ED73-4BAB-BF01-F7D1071B3580}"/>
+    <hyperlink ref="F30" r:id="rId67" xr:uid="{3833FE9B-16AC-4168-98A0-F366A5F5931C}"/>
+    <hyperlink ref="F31" r:id="rId68" xr:uid="{9E0268A9-6132-4557-AC30-84C3431F7FF7}"/>
+    <hyperlink ref="F32" r:id="rId69" xr:uid="{D2C105FA-916E-4BF1-9D4F-A1C259E809FF}"/>
+    <hyperlink ref="F33" r:id="rId70" xr:uid="{DB31F5E7-4580-4EFB-A312-280D8FC8E0D0}"/>
+    <hyperlink ref="F34" r:id="rId71" xr:uid="{07304E71-1E0C-47CB-882C-B6CA74783C8B}"/>
+    <hyperlink ref="F35" r:id="rId72" xr:uid="{715C5834-7FFF-4C31-87A7-FF7739A4982C}"/>
+    <hyperlink ref="F36" r:id="rId73" xr:uid="{C6AF7D36-67BA-4C84-A669-B3CC706CCF69}"/>
+    <hyperlink ref="F38" r:id="rId74" xr:uid="{F4DA861A-D2F6-469F-A199-AAC71FE25DB5}"/>
+    <hyperlink ref="F39" r:id="rId75" xr:uid="{7CF3CAE6-32B9-4F9D-BB32-B350977CA37A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
